--- a/main/ig/StructureDefinition-esms-consent.xlsx
+++ b/main/ig/StructureDefinition-esms-consent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T16:16:52+00:00</t>
+    <t>2026-06-25T13:33:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-esms-consent.xlsx
+++ b/main/ig/StructureDefinition-esms-consent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T13:33:01+00:00</t>
+    <t>2026-06-25T13:36:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-esms-consent.xlsx
+++ b/main/ig/StructureDefinition-esms-consent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T13:36:54+00:00</t>
+    <t>2026-06-26T14:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-esms-consent.xlsx
+++ b/main/ig/StructureDefinition-esms-consent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T14:17:25+00:00</t>
+    <t>2026-06-26T14:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-esms-consent.xlsx
+++ b/main/ig/StructureDefinition-esms-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.0.6</t>
+    <t>4.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T14:37:44+00:00</t>
+    <t>2026-06-29T07:12:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-esms-consent.xlsx
+++ b/main/ig/StructureDefinition-esms-consent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T07:12:03+00:00</t>
+    <t>2026-06-29T08:05:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-esms-consent.xlsx
+++ b/main/ig/StructureDefinition-esms-consent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:05:43+00:00</t>
+    <t>2026-06-29T08:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-esms-consent.xlsx
+++ b/main/ig/StructureDefinition-esms-consent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:06:46+00:00</t>
+    <t>2026-06-29T08:11:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-esms-consent.xlsx
+++ b/main/ig/StructureDefinition-esms-consent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:11:30+00:00</t>
+    <t>2026-06-29T08:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-esms-consent.xlsx
+++ b/main/ig/StructureDefinition-esms-consent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:20:47+00:00</t>
+    <t>2026-06-29T08:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
